--- a/Result/profitability/8011.xlsx
+++ b/Result/profitability/8011.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.495</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>21.91</v>
+        <v>22.435</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.53125</v>
+        <v>0.34625</v>
       </c>
       <c r="N3" t="n">
-        <v>20.945</v>
+        <v>21.08375</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4525</v>
+        <v>0.415</v>
       </c>
       <c r="N4" t="n">
-        <v>20.25125</v>
+        <v>19.11</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5575000000000001</v>
+        <v>0.5437500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.1475</v>
+        <v>19.01125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6175</v>
+        <v>0.6075</v>
       </c>
       <c r="N6" t="n">
-        <v>19.49625</v>
+        <v>20.06375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.97</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7075</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>19.995</v>
+        <v>19.6675</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.87875</v>
       </c>
       <c r="N8" t="n">
-        <v>20.46125</v>
+        <v>21.3275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9453,6 +9453,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>8011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>400</v>
+      </c>
+      <c r="D72" t="n">
+        <v>304</v>
+      </c>
+      <c r="E72" t="n">
+        <v>96</v>
+      </c>
+      <c r="F72" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="G72" t="n">
+        <v>41</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10.25%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>36</v>
+      </c>
+      <c r="K72" t="n">
+        <v>28</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N72" t="n">
+        <v>23.4975</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X72" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.4062133645955452</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.3928571428571429</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>-0.04346092503987242</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
